--- a/ITI/MHD/AssociationTypeVsRelatesTo.xlsx
+++ b/ITI/MHD/AssociationTypeVsRelatesTo.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>4.2.5-comment</t>
+    <t>4.2.5</t>
   </si>
   <si>
     <t>Name</t>
